--- a/docs/students/7a.xlsx
+++ b/docs/students/7a.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\María Alexandra\Listados Actualizados\LISTADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\AgenteIA_Alexandra\docs\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51B0A19-F7B3-4816-9988-0242138C6E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DDA360-3AE7-46F7-A0BC-30230EF61D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="113">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>23AC0237@cac.edu.co</t>
+  </si>
+  <si>
+    <t>ID_DRIVE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -490,37 +496,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -545,6 +520,37 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -556,7 +562,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -572,28 +578,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -935,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -943,9 +951,12 @@
     <col min="3" max="3" width="40.125" customWidth="1"/>
     <col min="4" max="4" width="45.875" customWidth="1"/>
     <col min="5" max="5" width="51.25" customWidth="1"/>
+    <col min="10" max="10" width="4" customWidth="1"/>
+    <col min="11" max="11" width="78.625" customWidth="1"/>
+    <col min="12" max="17" width="11.375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:11" ht="15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -961,15 +972,18 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="16"/>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -985,15 +999,18 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1009,15 +1026,18 @@
       <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="19"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1033,13 +1053,16 @@
       <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="19"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1055,15 +1078,18 @@
       <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -1079,15 +1105,18 @@
       <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="19"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
@@ -1101,13 +1130,16 @@
         <v>31</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -1123,15 +1155,18 @@
       <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1147,13 +1182,16 @@
       <c r="E9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -1169,15 +1207,18 @@
       <c r="E10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -1193,15 +1234,18 @@
       <c r="E11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="19"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -1217,15 +1261,18 @@
       <c r="E12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="19"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
@@ -1241,15 +1288,18 @@
       <c r="E13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="19"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -1270,8 +1320,11 @@
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
       <c r="J14" s="19"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
@@ -1287,15 +1340,18 @@
       <c r="E15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="19"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
@@ -1311,15 +1367,18 @@
       <c r="E16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="19"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.75">
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75">
       <c r="A17" s="7" t="s">
         <v>75</v>
       </c>
@@ -1333,15 +1392,18 @@
         <v>77</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="19"/>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>78</v>
       </c>
@@ -1357,15 +1419,18 @@
       <c r="E18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>83</v>
       </c>
@@ -1388,8 +1453,11 @@
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10" hidden="1">
+      <c r="K19" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" hidden="1">
       <c r="A20" s="12" t="s">
         <v>88</v>
       </c>
@@ -1405,20 +1473,29 @@
       <c r="E20" s="12" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" hidden="1">
+      <c r="K20" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" hidden="1">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-    </row>
-    <row r="22" spans="1:10" ht="0.95" hidden="1" customHeight="1">
+      <c r="K21" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="0.95" hidden="1" customHeight="1">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
+      <c r="K22" s="11" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -1498,14 +1575,26 @@
     <hyperlink ref="F15" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
     <hyperlink ref="F18" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
     <hyperlink ref="F19" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K2" r:id="rId52" xr:uid="{BF4420E6-6481-403B-B72A-BDEFC688D41F}"/>
+    <hyperlink ref="K3:K13" r:id="rId53" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{EF37C8C5-A0FF-4D21-980D-175B2ECF493A}"/>
+    <hyperlink ref="K14:K22" r:id="rId54" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{69BCE5FB-C6EC-4B22-B986-5B523C3BC6B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId52"/>
-  <legacyDrawing r:id="rId53"/>
+  <pageSetup orientation="portrait" r:id="rId55"/>
+  <legacyDrawing r:id="rId56"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010033786E0F47F2E4479E1418699C7D1887" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8889b9d8e9583677ca2221be300ac5d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b44af97c-a663-43df-bc64-dfb44812992d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c5274dc35b9ea6c79ecd381a4eab1a6" ns2:_="">
     <xsd:import namespace="b44af97c-a663-43df-bc64-dfb44812992d"/>
@@ -1643,22 +1732,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBBEA71-C632-4AE8-B7C8-3F289DADFCB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{196073E8-6B75-4A3D-94ED-1A629E1F09BE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1676,19 +1764,11 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35073413-9516-4B73-8842-99BBF230AC45}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBBEA71-C632-4AE8-B7C8-3F289DADFCB3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>